--- a/templates/data-worksheets.xlsx
+++ b/templates/data-worksheets.xlsx
@@ -465,7 +465,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -671,6 +671,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -678,7 +679,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -811,6 +812,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -818,7 +820,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -927,6 +929,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -934,7 +937,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1035,5 +1038,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>